--- a/17 18 20/Excel/6.Project/Inventory Managment/Practice/CountIFS.xlsx
+++ b/17 18 20/Excel/6.Project/Inventory Managment/Practice/CountIFS.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="10">
   <si>
     <t>Code</t>
   </si>
@@ -58,7 +58,162 @@
     <t>Count of Cut_off</t>
   </si>
   <si>
-    <t>countifs(CriteriaRange_01,Cri_01,CriteriaRange_02,Cri_02)</t>
+    <r>
+      <t xml:space="preserve">countifs(
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CriteriaRange_01,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Cri_01,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>CriteriaRange_02,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>Cri_02</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">=COUNTIFS(
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>MSF[[#All],[Code]]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>Sheet3!$H16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>MSF[[#All],[Cut_off]]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>Sheet3!$I$14</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -70,7 +225,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,9 +273,36 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="9" tint="0.39997558519241921"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -200,7 +382,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -208,15 +390,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
@@ -799,52 +991,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A3:T22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="M1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+    </row>
+    <row r="4" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -857,18 +1040,27 @@
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="3">
-        <v>46219</v>
-      </c>
-      <c r="L4">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!J4,MSF[[#All],[Cut_off]],Sheet3!K4)</f>
+      <c r="I4" s="3">
+        <v>46219</v>
+      </c>
+      <c r="J4">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!H4,MSF[[#All],[Cut_off]],Sheet3!I4)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -881,18 +1073,27 @@
       <c r="D5" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="3">
+      <c r="I5" s="3">
         <v>46220</v>
       </c>
-      <c r="L5">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!J5,MSF[[#All],[Cut_off]],Sheet3!K5)</f>
+      <c r="J5">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!H5,MSF[[#All],[Cut_off]],Sheet3!I5)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -903,18 +1104,27 @@
       <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="3">
-        <v>46219</v>
-      </c>
-      <c r="L6">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!J6,MSF[[#All],[Cut_off]],Sheet3!K6)</f>
+      <c r="I6" s="3">
+        <v>46219</v>
+      </c>
+      <c r="J6">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!H6,MSF[[#All],[Cut_off]],Sheet3!I6)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -925,18 +1135,27 @@
       <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="3">
-        <v>46219</v>
-      </c>
-      <c r="L7">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!J7,MSF[[#All],[Cut_off]],Sheet3!K7)</f>
+      <c r="I7" s="3">
+        <v>46219</v>
+      </c>
+      <c r="J7">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!H7,MSF[[#All],[Cut_off]],Sheet3!I7)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -947,18 +1166,27 @@
       <c r="D8" s="5">
         <v>3</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>46219</v>
-      </c>
-      <c r="L8">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!J8,MSF[[#All],[Cut_off]],Sheet3!K8)</f>
+      <c r="I8" s="3">
+        <v>46219</v>
+      </c>
+      <c r="J8">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!H8,MSF[[#All],[Cut_off]],Sheet3!I8)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -971,83 +1199,226 @@
       <c r="D9" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="K14" s="3">
-        <v>46219</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+    </row>
+    <row r="11" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+    </row>
+    <row r="12" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+    </row>
+    <row r="13" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+    </row>
+    <row r="14" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="3">
+        <v>46219</v>
+      </c>
+      <c r="J14" s="3">
         <v>46220</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="J15" s="6" t="s">
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+    </row>
+    <row r="15" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="J16" s="4" t="s">
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+    </row>
+    <row r="16" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K16" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J16,MSF[[#All],[Cut_off]],Sheet3!$K$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J16,Louvre[[#All],[Cut_off]],Sheet3!$K$14)</f>
+      <c r="I16" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H16,MSF[[#All],[Cut_off]],Sheet3!$I$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H16,Louvre[[#All],[Cut_off]],Sheet3!$I$14)</f>
         <v>4</v>
       </c>
-      <c r="L16" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J16,MSF[[#All],[Cut_off]],Sheet3!$L$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J16,Louvre[[#All],[Cut_off]],Sheet3!$L$14)</f>
+      <c r="J16" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H16,MSF[[#All],[Cut_off]],Sheet3!$J$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H16,Louvre[[#All],[Cut_off]],Sheet3!$J$14)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J17" s="4" t="s">
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+    </row>
+    <row r="17" spans="8:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J17,MSF[[#All],[Cut_off]],Sheet3!$K$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J17,Louvre[[#All],[Cut_off]],Sheet3!$K$14)</f>
+      <c r="I17" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H17,MSF[[#All],[Cut_off]],Sheet3!$I$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H17,Louvre[[#All],[Cut_off]],Sheet3!$I$14)</f>
         <v>4</v>
       </c>
-      <c r="L17" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J17,MSF[[#All],[Cut_off]],Sheet3!$L$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J17,Louvre[[#All],[Cut_off]],Sheet3!$L$14)</f>
+      <c r="J17" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H17,MSF[[#All],[Cut_off]],Sheet3!$J$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H17,Louvre[[#All],[Cut_off]],Sheet3!$J$14)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J18" s="4" t="s">
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+    </row>
+    <row r="18" spans="8:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K18" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J18,MSF[[#All],[Cut_off]],Sheet3!$K$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J18,Louvre[[#All],[Cut_off]],Sheet3!$K$14)</f>
+      <c r="I18" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H18,MSF[[#All],[Cut_off]],Sheet3!$I$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H18,Louvre[[#All],[Cut_off]],Sheet3!$I$14)</f>
         <v>6</v>
       </c>
-      <c r="L18" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J18,MSF[[#All],[Cut_off]],Sheet3!$L$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J18,Louvre[[#All],[Cut_off]],Sheet3!$L$14)</f>
+      <c r="J18" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H18,MSF[[#All],[Cut_off]],Sheet3!$J$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H18,Louvre[[#All],[Cut_off]],Sheet3!$J$14)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J19" s="4" t="s">
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+    </row>
+    <row r="19" spans="8:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K19" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J19,MSF[[#All],[Cut_off]],Sheet3!$K$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J19,Louvre[[#All],[Cut_off]],Sheet3!$K$14)</f>
+      <c r="I19" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H19,MSF[[#All],[Cut_off]],Sheet3!$I$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H19,Louvre[[#All],[Cut_off]],Sheet3!$I$14)</f>
         <v>6</v>
       </c>
-      <c r="L19" s="13">
-        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$J19,MSF[[#All],[Cut_off]],Sheet3!$L$14)+
-COUNTIFS(Louvre[[#All],[Code]],Sheet3!$J19,Louvre[[#All],[Cut_off]],Sheet3!$L$14)</f>
+      <c r="J19" s="12">
+        <f>COUNTIFS(MSF[[#All],[Code]],Sheet3!$H19,MSF[[#All],[Cut_off]],Sheet3!$J$14)+
+COUNTIFS(Louvre[[#All],[Code]],Sheet3!$H19,Louvre[[#All],[Cut_off]],Sheet3!$J$14)</f>
         <v>0</v>
       </c>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+    </row>
+    <row r="20" spans="8:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+    </row>
+    <row r="21" spans="8:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+    </row>
+    <row r="22" spans="8:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="M1:S2"/>
+  <mergeCells count="2">
+    <mergeCell ref="L3:R8"/>
+    <mergeCell ref="L11:R17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1064,15 +1435,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="1">
@@ -1080,7 +1451,7 @@
       </c>
     </row>
     <row r="3" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M3" s="1">
@@ -1088,7 +1459,7 @@
       </c>
     </row>
     <row r="4" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="1">
@@ -1096,7 +1467,7 @@
       </c>
     </row>
     <row r="5" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="M5" s="1">
@@ -1104,7 +1475,7 @@
       </c>
     </row>
     <row r="6" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>5</v>
       </c>
       <c r="M6" s="1">
@@ -1112,7 +1483,7 @@
       </c>
     </row>
     <row r="7" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="1">
@@ -1120,7 +1491,7 @@
       </c>
     </row>
     <row r="8" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M8" s="1">
@@ -1128,7 +1499,7 @@
       </c>
     </row>
     <row r="9" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M9" s="1">
@@ -1136,7 +1507,7 @@
       </c>
     </row>
     <row r="10" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="1">
@@ -1144,7 +1515,7 @@
       </c>
     </row>
     <row r="11" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>3</v>
       </c>
       <c r="M11" s="1">
@@ -1152,10 +1523,10 @@
       </c>
     </row>
     <row r="12" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="11">
         <v>46219</v>
       </c>
     </row>
